--- a/02_여행데이터/202607_스페인포르투갈_확정내역.xlsx
+++ b/02_여행데이터/202607_스페인포르투갈_확정내역.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\여행\20260716~0731 스페인 포르투갈\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lovem\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272439FB-E52E-4D48-9AB1-2DA25976A269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F770E48C-E8DC-45A8-B549-7D0CBC93EA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{458CB61D-10E5-435F-9A83-F7A396155C88}"/>
+    <workbookView xWindow="5980" yWindow="4520" windowWidth="28800" windowHeight="15380" xr2:uid="{458CB61D-10E5-435F-9A83-F7A396155C88}"/>
   </bookViews>
   <sheets>
     <sheet name="필수예약" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="119">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -386,10 +386,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0923000559</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>인천공항 출발</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -507,6 +503,10 @@
   </si>
   <si>
     <t>가우디,예약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>숙소 체크아웃</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -921,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{058C4E13-2DB6-4788-96D2-DAF65710BD31}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.4140625" style="1" customWidth="1"/>
@@ -962,7 +962,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
@@ -979,7 +979,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
@@ -1005,7 +1005,7 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
@@ -1031,7 +1031,7 @@
         <v>7.9861111111111105E-2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>0.40277777777777779</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>0.625</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
@@ -1115,13 +1115,13 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>12</v>
@@ -1147,7 +1147,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>10</v>
@@ -1173,13 +1173,13 @@
         <v>0.375</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>12</v>
@@ -1205,13 +1205,13 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>12</v>
@@ -1237,13 +1237,13 @@
         <v>0.6875</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>12</v>
@@ -1295,7 +1295,7 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>10</v>
@@ -1327,7 +1327,7 @@
         <v>0.55902777777777779</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>0.625</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>17</v>
@@ -1389,7 +1389,7 @@
         <v>0.375</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>21</v>
@@ -1421,7 +1421,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>17</v>
@@ -1511,7 +1511,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>21</v>
@@ -1537,7 +1537,7 @@
         <v>0.8125</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>21</v>
@@ -1569,7 +1569,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
@@ -1601,7 +1601,7 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>0.625</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>17</v>
@@ -1659,7 +1659,7 @@
         <v>0.36458333333333331</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>0.5</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>10</v>
@@ -1721,7 +1721,7 @@
         <v>0.625</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>17</v>
@@ -1750,7 +1750,7 @@
         <v>0.8125</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>21</v>
@@ -1782,7 +1782,7 @@
         <v>0.31944444444444442</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>10</v>
@@ -1814,7 +1814,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>2.4305555555555556E-2</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>10</v>
@@ -1878,7 +1878,7 @@
         <v>0.73263888888888884</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>10</v>
@@ -1907,7 +1907,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>10</v>
@@ -1936,7 +1936,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>10</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>9</v>
@@ -1965,7 +1965,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>17</v>
@@ -1979,8 +1979,32 @@
       <c r="H35" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>88</v>
+      <c r="I35" s="6"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A36" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
